--- a/artfynd/A 30179-2026 artfynd.xlsx
+++ b/artfynd/A 30179-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445013</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445029</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444533</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445403</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1632,6 +1677,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444952</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445609</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135444544</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445444</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445431</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445436</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445034</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,6 +2457,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445041</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2483,6 +2568,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445081</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2589,6 +2679,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445419</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,8 +2790,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30179-2026 artfynd.xlsx
+++ b/artfynd/A 30179-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445013</v>
       </c>
       <c r="B2" t="n">
-        <v>90913</v>
+        <v>90955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135444418</v>
       </c>
       <c r="B3" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135445029</v>
       </c>
       <c r="B4" t="n">
-        <v>75468</v>
+        <v>75504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135444751</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135444533</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135444729</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135444848</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>135445403</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135444952</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135445609</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135444544</v>
       </c>
       <c r="B12" t="n">
-        <v>8460</v>
+        <v>8461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135445444</v>
       </c>
       <c r="B13" t="n">
-        <v>56842</v>
+        <v>56847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>135445431</v>
       </c>
       <c r="B14" t="n">
-        <v>58812</v>
+        <v>58817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>135445436</v>
       </c>
       <c r="B15" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135445034</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135445041</v>
       </c>
       <c r="B17" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>135445081</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135445419</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135445424</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30179-2026 artfynd.xlsx
+++ b/artfynd/A 30179-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445013</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>90982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135444418</v>
       </c>
       <c r="B3" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135445029</v>
       </c>
       <c r="B4" t="n">
-        <v>75504</v>
+        <v>75531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135444751</v>
       </c>
       <c r="B5" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135445034</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135445041</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>135445081</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135445419</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135445424</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30179-2026 artfynd.xlsx
+++ b/artfynd/A 30179-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445013</v>
       </c>
       <c r="B2" t="n">
-        <v>90985</v>
+        <v>90987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135444418</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135445034</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135445041</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>135445081</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135445419</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135445424</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30179-2026 artfynd.xlsx
+++ b/artfynd/A 30179-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135445013</v>
       </c>
       <c r="B2" t="n">
-        <v>90987</v>
+        <v>90989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135444418</v>
       </c>
       <c r="B3" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>135445029</v>
       </c>
       <c r="B4" t="n">
-        <v>75531</v>
+        <v>75533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135444751</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>135444533</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135444729</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>135444848</v>
       </c>
       <c r="B8" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>135445403</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135444952</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>135445609</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>135444544</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135445444</v>
       </c>
       <c r="B13" t="n">
-        <v>56847</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>135445431</v>
       </c>
       <c r="B14" t="n">
-        <v>58817</v>
+        <v>58819</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>135445436</v>
       </c>
       <c r="B15" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>135445034</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>135445041</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>135445081</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>135445419</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135445424</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
